--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 11:56</t>
+          <t>更新时间: 2026-08-06 11:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 11:59</t>
+          <t>更新时间: 2026-08-07 11:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-07 11:43</t>
+          <t>更新时间: 2026-08-08 10:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 10:51</t>
+          <t>更新时间: 2026-08-09 10:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-09 10:58</t>
+          <t>更新时间: 2026-08-10 11:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-10 11:07</t>
+          <t>更新时间: 2026-08-11 11:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-11 11:00</t>
+          <t>更新时间: 2026-08-12 11:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 11:19</t>
+          <t>更新时间: 2026-08-13 11:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-13 11:28</t>
+          <t>更新时间: 2026-08-14 11:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 11:20</t>
+          <t>更新时间: 2026-08-15 10:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 10:09</t>
+          <t>更新时间: 2026-08-16 10:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 10:17</t>
+          <t>更新时间: 2026-08-17 10:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 10:15</t>
+          <t>更新时间: 2026-08-18 10:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 10:10</t>
+          <t>更新时间: 2026-08-19 10:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 10:13</t>
+          <t>更新时间: 2026-08-20 10:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 10:12</t>
+          <t>更新时间: 2026-08-21 10:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 10:19</t>
+          <t>更新时间: 2026-08-22 10:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 10:10</t>
+          <t>更新时间: 2026-08-23 10:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 10:19</t>
+          <t>更新时间: 2026-08-24 10:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 10:18</t>
+          <t>更新时间: 2026-08-25 10:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 10:19</t>
+          <t>更新时间: 2026-08-26 10:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 10:20</t>
+          <t>更新时间: 2026-08-27 18:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 18:47</t>
+          <t>更新时间: 2026-08-28 20:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 20:24</t>
+          <t>更新时间: 2026-08-29 15:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 15:33</t>
+          <t>更新时间: 2026-08-30 14:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 14:06</t>
+          <t>更新时间: 2026-08-31 14:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 14:28</t>
+          <t>更新时间: 2026-09-01 13:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 13:54</t>
+          <t>更新时间: 2026-09-02 13:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 13:17</t>
+          <t>更新时间: 2026-09-03 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:22</t>
+          <t>更新时间: 2026-09-04 13:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:17</t>
+          <t>更新时间: 2026-09-05 13:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:06</t>
+          <t>更新时间: 2026-09-06 13:21</t>
         </is>
       </c>
     </row>
